--- a/docs/dasu-kb-shortcuts.xlsx
+++ b/docs/dasu-kb-shortcuts.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,12 +46,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00EBEBF0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -115,12 +109,6 @@
       <color rgb="000A84FF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -161,7 +149,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F5F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F2F2F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDF5E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,16 +170,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDE8FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF5E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -225,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -239,148 +227,145 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -748,11 +733,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
@@ -762,25 +747,18 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dasu.print — Keyboard Shortcuts Reference  v0.2.0</t>
+          <t>Dasu.print — Keyboard Shortcuts Reference  v0.4.0-alpha</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>出す · Open in Edge as a local file (file:///C:/dasu/dasu.html) for all shortcuts to work</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="8" customHeight="1">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-    </row>
+          <t>Open as local file in Edge/Chrome (file:///C:/dasu/dasu.html) for all shortcuts to work</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -935,7 +913,7 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Hold Alt, drag with left mouse button</t>
+          <t>Hold Alt, drag with left button</t>
         </is>
       </c>
       <c r="F10" s="11" t="inlineStr">
@@ -947,12 +925,12 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Middle mouse drag</t>
+          <t>Space (hold)</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Pan canvas</t>
+          <t>Temporary pan mode</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -967,7 +945,7 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Alternative pan method</t>
+          <t>Hold Space, drag to pan</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -979,12 +957,12 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Space (hold)</t>
+          <t>Middle mouse drag</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Temporary pan mode</t>
+          <t>Pan canvas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -992,16 +970,12 @@
           <t>Navigation</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Hold Space, drag to pan, release to restore tool</t>
-        </is>
-      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="10" t="inlineStr">
         <is>
           <t>None</t>
@@ -1011,395 +985,391 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  View</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Toggle grid on / off</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Toggle snap on / off</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Selection</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Click</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Select element</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Selection</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>Select tool must be active</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Ctrl + A</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Select all elements</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Selection</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>Non-locked, non-sheet elements</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Esc</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>Cancel tool / deselect</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>Selection</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>Also exits text editing</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Editing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Del / Backspace</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Delete selected</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>Editing</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr"/>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + Z</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Undo</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>Editing</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
         <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Esc</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>Cancel tool / deselect</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Selection</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>Also exits text editing mode</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Editing</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Del / Backspace</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>Delete selected element</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>Wired in menu, not yet implemented</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + Y</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Redo</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Editing</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr"/>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>Ctrl + Z</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>Undo</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
+          <t>Wired in menu, not yet implemented</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + C</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Copy element to internal clipboard</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Editing</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>Wired in menu, not yet implemented</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Ctrl + Y</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>Redo</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>Internal clipboard only</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + V</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Paste internal clipboard element</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Editing</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>Wired in menu, not yet implemented</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>Ctrl + C</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>Copy selected element</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
+          <t>Works across sheets</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + V</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Paste from OS clipboard</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Editing</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>Works across sheets</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>Ctrl + V</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>Paste element or OS clipboard</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>Images (screenshots) and plain text</t>
+        </is>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Ctrl + D</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Duplicate selected element</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Editing</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>Pastes element copy or image/text from OS</t>
-        </is>
-      </c>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Ctrl + D</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>Duplicate selected element</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>Editing</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>Places copy with small offset</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Nudge</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>Arrow keys</t>
-        </is>
-      </c>
-      <c r="B28" s="24" t="inlineStr">
-        <is>
-          <t>Nudge element (small)</t>
-        </is>
-      </c>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>Nudge</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E28" s="26" t="inlineStr">
-        <is>
-          <t>Default 1 mm</t>
-        </is>
-      </c>
-      <c r="F28" s="27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Shift + Arrow</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Nudge element (large) + snap</t>
-        </is>
-      </c>
-      <c r="C29" s="25" t="inlineStr">
-        <is>
-          <t>Nudge</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E29" s="26" t="inlineStr">
-        <is>
-          <t>Default 4× nudge distance</t>
-        </is>
-      </c>
-      <c r="F29" s="27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>Ctrl + Arrow</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>Nudge element (large)</t>
-        </is>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
-        <is>
-          <t>Nudge</t>
-        </is>
-      </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
       </c>
-      <c r="E30" s="26" t="inlineStr">
-        <is>
-          <t>Large nudge without snap</t>
-        </is>
-      </c>
-      <c r="F30" s="27" t="inlineStr">
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>10mm offset from original</t>
+        </is>
+      </c>
+      <c r="F30" s="26" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -1408,24 +1378,24 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Draw</t>
+          <t xml:space="preserve">  Order</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>Shift + drag</t>
+          <t>Ctrl + ]</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>Snaps active while dragging</t>
+          <t>Bring forward one step</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1435,7 +1405,7 @@
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
-          <t>Smart guides + grid snap</t>
+          <t>Never goes behind sheet background</t>
         </is>
       </c>
       <c r="F33" s="32" t="inlineStr">
@@ -1447,17 +1417,17 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>Ctrl + drag</t>
+          <t>Ctrl + [</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Ortho lock while dragging</t>
+          <t>Send backward one step</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1467,7 +1437,7 @@
       </c>
       <c r="E34" s="31" t="inlineStr">
         <is>
-          <t>Constrains to horizontal or vertical</t>
+          <t>Never goes behind sheet background</t>
         </is>
       </c>
       <c r="F34" s="32" t="inlineStr">
@@ -1479,17 +1449,17 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>Shift + line drag</t>
+          <t>Ctrl + Shift + ]</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>Angle snap (line tool)</t>
+          <t>Bring to front</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1497,11 +1467,7 @@
           <t>LIVE</t>
         </is>
       </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>Snaps to 15° increments by default</t>
-        </is>
-      </c>
+      <c r="E35" s="31" t="inlineStr"/>
       <c r="F35" s="32" t="inlineStr">
         <is>
           <t>None</t>
@@ -1511,17 +1477,17 @@
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
-          <t>Alt + click (line)</t>
+          <t>Ctrl + Shift + [</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Finish polyline</t>
+          <t>Send to back</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Order</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -1531,7 +1497,7 @@
       </c>
       <c r="E36" s="31" t="inlineStr">
         <is>
-          <t>Completes open polyline</t>
+          <t>Always above sheet background</t>
         </is>
       </c>
       <c r="F36" s="32" t="inlineStr">
@@ -1540,97 +1506,101 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>C (polyline)</t>
-        </is>
-      </c>
-      <c r="B37" s="29" t="inlineStr">
-        <is>
-          <t>Close polygon</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>Closes polyline to form polygon</t>
-        </is>
-      </c>
-      <c r="F37" s="32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>Enter (polyline)</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="inlineStr">
-        <is>
-          <t>Finish polyline / polygon</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="inlineStr">
-        <is>
-          <t>Draw</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E38" s="31" t="inlineStr"/>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Nudge</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>Arrow keys</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>Nudge element (small)</t>
+        </is>
+      </c>
+      <c r="C39" s="35" t="inlineStr">
+        <is>
+          <t>Nudge</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>Default 1 mm</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Dimension</t>
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>Shift + Arrow</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>Nudge element (large) + snap</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Nudge</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E40" s="36" t="inlineStr">
+        <is>
+          <t>4x nudge distance</t>
+        </is>
+      </c>
+      <c r="F40" s="37" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="33" t="inlineStr">
         <is>
-          <t>H (dim tool)</t>
+          <t>Ctrl + Arrow</t>
         </is>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>Force horizontal dimension</t>
+          <t>Nudge element (large)</t>
         </is>
       </c>
       <c r="C41" s="35" t="inlineStr">
         <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
+          <t>Nudge</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="E41" s="36" t="inlineStr">
         <is>
-          <t>After first point pick</t>
+          <t>Large nudge without snap</t>
         </is>
       </c>
       <c r="F41" s="37" t="inlineStr">
@@ -1639,99 +1609,103 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="33" t="inlineStr">
-        <is>
-          <t>V (dim tool)</t>
-        </is>
-      </c>
-      <c r="B42" s="34" t="inlineStr">
-        <is>
-          <t>Force vertical dimension</t>
-        </is>
-      </c>
-      <c r="C42" s="35" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E42" s="36" t="inlineStr">
-        <is>
-          <t>After first point pick</t>
-        </is>
-      </c>
-      <c r="F42" s="37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="33" t="inlineStr">
-        <is>
-          <t>Ctrl (dim tool)</t>
-        </is>
-      </c>
-      <c r="B43" s="34" t="inlineStr">
-        <is>
-          <t>Ortho lock — auto H or V</t>
-        </is>
-      </c>
-      <c r="C43" s="35" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E43" s="36" t="inlineStr">
-        <is>
-          <t>Hold Ctrl on second click, angle determines H/V</t>
-        </is>
-      </c>
-      <c r="F43" s="37" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Draw</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>Shift + drag</t>
+        </is>
+      </c>
+      <c r="B44" s="39" t="inlineStr">
+        <is>
+          <t>Snaps active while dragging</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E44" s="41" t="inlineStr">
+        <is>
+          <t>Smart guides + grid snap</t>
+        </is>
+      </c>
+      <c r="F44" s="42" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Order</t>
+      <c r="A45" s="38" t="inlineStr">
+        <is>
+          <t>Ctrl + drag</t>
+        </is>
+      </c>
+      <c r="B45" s="39" t="inlineStr">
+        <is>
+          <t>Ortho lock while dragging</t>
+        </is>
+      </c>
+      <c r="C45" s="40" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>Constrains to H or V</t>
+        </is>
+      </c>
+      <c r="F45" s="42" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t>Ctrl + ]</t>
+          <t>Shift + rotate</t>
         </is>
       </c>
       <c r="B46" s="39" t="inlineStr">
         <is>
-          <t>Bring forward one step</t>
+          <t>Snap rotation to angle increment</t>
         </is>
       </c>
       <c r="C46" s="40" t="inlineStr">
         <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E46" s="41" t="inlineStr"/>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>Uses lineAngleSnap setting (default 15 deg)</t>
+        </is>
+      </c>
       <c r="F46" s="42" t="inlineStr">
         <is>
           <t>None</t>
@@ -1741,25 +1715,29 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="38" t="inlineStr">
         <is>
-          <t>Ctrl + [</t>
+          <t>Shift (line tool)</t>
         </is>
       </c>
       <c r="B47" s="39" t="inlineStr">
         <is>
-          <t>Send backward one step</t>
+          <t>Angle snap</t>
         </is>
       </c>
       <c r="C47" s="40" t="inlineStr">
         <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E47" s="41" t="inlineStr"/>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
+        <is>
+          <t>Snaps to 15 deg increments</t>
+        </is>
+      </c>
       <c r="F47" s="42" t="inlineStr">
         <is>
           <t>None</t>
@@ -1769,22 +1747,22 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t>Ctrl + Shift + ]</t>
+          <t>Alt + click (line)</t>
         </is>
       </c>
       <c r="B48" s="39" t="inlineStr">
         <is>
-          <t>Bring to front</t>
+          <t>Finish polyline</t>
         </is>
       </c>
       <c r="C48" s="40" t="inlineStr">
         <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="E48" s="41" t="inlineStr"/>
@@ -1797,22 +1775,22 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>Ctrl + Shift + [</t>
+          <t>C (polyline)</t>
         </is>
       </c>
       <c r="B49" s="39" t="inlineStr">
         <is>
-          <t>Send to back</t>
+          <t>Close polygon</t>
         </is>
       </c>
       <c r="C49" s="40" t="inlineStr">
         <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
       <c r="E49" s="41" t="inlineStr"/>
@@ -1822,340 +1800,387 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  View</t>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="38" t="inlineStr">
+        <is>
+          <t>Enter (polyline)</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>Finish polyline</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr"/>
+      <c r="F50" s="42" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="43" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="B52" s="44" t="inlineStr">
-        <is>
-          <t>Toggle grid on / off</t>
-        </is>
-      </c>
-      <c r="C52" s="45" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="E52" s="46" t="inlineStr"/>
-      <c r="F52" s="47" t="inlineStr">
-        <is>
-          <t>None</t>
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Dimension</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>H (dim tool)</t>
         </is>
       </c>
       <c r="B53" s="44" t="inlineStr">
         <is>
-          <t>Toggle snap on / off</t>
+          <t>Force horizontal dimension</t>
         </is>
       </c>
       <c r="C53" s="45" t="inlineStr">
         <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>After first point pick</t>
+        </is>
+      </c>
+      <c r="F53" s="47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="43" t="inlineStr">
+        <is>
+          <t>V (dim tool)</t>
+        </is>
+      </c>
+      <c r="B54" s="44" t="inlineStr">
+        <is>
+          <t>Force vertical dimension</t>
+        </is>
+      </c>
+      <c r="C54" s="45" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>After first point pick</t>
+        </is>
+      </c>
+      <c r="F54" s="47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t>Ctrl (dim tool)</t>
+        </is>
+      </c>
+      <c r="B55" s="44" t="inlineStr">
+        <is>
+          <t>Ortho lock - auto H or V</t>
+        </is>
+      </c>
+      <c r="C55" s="45" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E55" s="46" t="inlineStr">
+        <is>
+          <t>Hold on second click</t>
+        </is>
+      </c>
+      <c r="F55" s="47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  File</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + N</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E58" s="20" t="inlineStr"/>
+      <c r="F58" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + O</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>Open .bprint file</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E59" s="20" t="inlineStr"/>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + S</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr"/>
+      <c r="F60" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + S</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>Save As</t>
+        </is>
+      </c>
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr"/>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + Shift + E</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>Export PDF</t>
+        </is>
+      </c>
+      <c r="C62" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr"/>
+      <c r="F62" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + P</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr"/>
+      <c r="F63" s="48" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Ctrl + ,</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>Preferences</t>
+        </is>
+      </c>
+      <c r="C64" s="19" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr"/>
+      <c r="F64" s="21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="49" t="inlineStr">
+        <is>
+          <t>Status Legend</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="50" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>Implemented and working in v0.4.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="51" t="inlineStr">
         <is>
           <t>PLANNED</t>
         </is>
       </c>
-      <c r="E53" s="46" t="inlineStr"/>
-      <c r="F53" s="47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  File</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + N</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>New sheet / open start dialog</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E56" s="16" t="inlineStr"/>
-      <c r="F56" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + O</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Open .bprint file</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="inlineStr"/>
-      <c r="F57" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + S</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Save</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>Opens Save As on first save</t>
-        </is>
-      </c>
-      <c r="F58" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + S</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Save As</t>
-        </is>
-      </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>Opens folder picker dialog</t>
-        </is>
-      </c>
-      <c r="F59" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + Shift + E</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Export PDF</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="inlineStr"/>
-      <c r="F60" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + P</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr"/>
-      <c r="F61" s="48" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl + ,</t>
-        </is>
-      </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>Preferences</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>File</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr"/>
-      <c r="F62" s="17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="A64" s="49" t="inlineStr">
-        <is>
-          <t>Status Legend</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="50" t="inlineStr">
-        <is>
-          <t>LIVE</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Implemented and working in current version</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="A66" s="51" t="inlineStr">
-        <is>
-          <t>PLANNED</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Specified for next sprint — not yet implemented</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="52" t="inlineStr">
-        <is>
-          <t>FUTURE</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>On the roadmap but not yet scheduled</t>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Specified for next sprint</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B65:F65"/>
+  <mergeCells count="14">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="B66:F66"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
